--- a/Statewise_center.xlsx
+++ b/Statewise_center.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\chataddb\stubot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FDA02AA-04ED-4BC1-921A-9D4D984B67F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79415888-757B-404E-9CB9-70C97FA41811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F354BEE7-42A4-43B2-8253-A83913595CD1}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$241</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$241</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -3101,7 +3101,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A241" xr:uid="{3907EB7E-1BE4-4681-BC79-EF31BC09E0E0}"/>
+  <autoFilter ref="A1:B241" xr:uid="{3907EB7E-1BE4-4681-BC79-EF31BC09E0E0}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>